--- a/光伏配储项目/电价数据/2026/揭阳站.xlsx
+++ b/光伏配储项目/电价数据/2026/揭阳站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.35521</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.8712799999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.38438</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.40925</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.36741</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.41222</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.35123</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.33851</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.34766</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.33375</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.35364</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.33685</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30833</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31242</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.31529</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.27148</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.37597</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.4331</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.08577</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.18366</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.29002</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.26488</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.26936</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.25418</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.42573</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.87393</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.50739</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.5207000000000001</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.33645</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6100599999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.59111</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7612899999999999</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.16031</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39958</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.63163</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44685</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.68186</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.92371</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5443</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.22942</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.39703</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.11952</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.12903</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.34696</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.44515</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.47267</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.7367999999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.79157</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.24233</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.9355</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.9586399999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.82072</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.79011</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5333</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.5102599999999999</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.48764</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42995</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.44147</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.77863</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.96211</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.06926</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.54889</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5676100000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5581499999999999</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.55838</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.5374</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.51463</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.39735</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.30515</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.29896</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3046</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.21662</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.17912</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.23396</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.33693</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.39704</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.48838</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30685</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.37101</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.5549500000000001</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.5536</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.7349</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6982</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.94364</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.37942</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.37156</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.44988</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.8745700000000001</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.56671</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.48281</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.41531</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.7328600000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.4365</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.05695</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.64634</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.8513099999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.9292999999999999</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.25451</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.71605</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.18236</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.9301699999999999</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.2796</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.1638</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.35083</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.07958</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.14839</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.70985</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.04583</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.96865</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.02527</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.89747</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.14661</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.9694199999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.46715</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.91904</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.9838</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.46535</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.44165</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.45922</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38837</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33728</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.55272</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5273099999999999</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.39666</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.48003</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.43999</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.40336</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37819</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.46204</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.48291</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.42178</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.38519</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.36478</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.51803</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.46689</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.4712</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.4142</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.12087</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.16037</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27028</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.35112</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.42167</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.07933</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>1.04401</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.8188200000000001</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.80162</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>1.03773</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>1.02758</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.99086</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.9957</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.89198</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.97682</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.92047</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.8911399999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.09392</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.57784</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.66584</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.86682</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.8895700000000001</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.73764</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.8030700000000001</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5542899999999999</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.00372</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.49646</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.40407</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45502</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.52198</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5329700000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.61846</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.67112</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.6826</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.68247</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.4561</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.65387</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.69569</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.47863</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51079</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.67327</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.85153</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.8171499999999999</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.9907999999999999</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.48348</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.68338</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.4662</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.55787</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.66938</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.8763099999999999</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.60754</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.0222</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.8001900000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.64711</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.59556</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.73585</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.44972</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.47178</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40537</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35355</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34509</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.55522</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.53322</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.46757</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.40809</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.40702</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40731</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3811</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.40416</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.37649</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.48083</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.37432</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.37254</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34557</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35571</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36352</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.40576</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35796</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38918</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42593</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.44627</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.36679</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.53613</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.35267</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.6881799999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.45292</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.45496</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.27417</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.6847799999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.40644</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.44449</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6939299999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.5898099999999999</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.48154</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.42519</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.49865</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.54884</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.76427</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.5525099999999999</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.57902</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.49711</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.41035</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.52599</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.63422</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.7551599999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.54264</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.65479</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.55013</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50281</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.49004</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.4632</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.44952</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.44382</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.37643</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.39319</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3151600000000001</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.36094</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31874</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31573</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30921</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31329</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28624</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.34665</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14276</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.32271</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02199</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.36501</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.41282</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.43766</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.2728</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.26094</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24628</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.11221</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.05868</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29736</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34276</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.33395</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3472</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.48158</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42133</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35099</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31515</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.42995</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.22827</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.2364</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.25824</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32558</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.18282</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.18365</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.24221</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.19424</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24321</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.20749</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.18475</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.16505</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24365</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.2657</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.19255</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26412</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09444</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03847</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04484</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.009779999999999999</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20575</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04904</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27475</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19722</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.42586</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.00736</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.0599</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05811</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31456</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30035</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.4604</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.43599</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.39255</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.44855</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.49073</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.46568</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7886599999999999</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18706</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.87025</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.64935</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57055</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20697</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.47395</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42932</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35266</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38582</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44324</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.3614</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.46281</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.6028300000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6418200000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.97985</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.51574</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28163</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.43111</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4087</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.6674600000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.91613</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26376</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.68147</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.52715</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31799</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30184</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32506</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30494</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.17112</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.25949</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.25881</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27404</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.2577</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.27837</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32255</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.28884</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.29867</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.29589</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.29983</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28499</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.3217</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.86778</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.38607</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30792</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.28997</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.2946</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29444</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.30425</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30474</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.37329</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.57874</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.51351</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.4905</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.43427</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.37152</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.24485</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29889</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.40582</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.39896</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.47713</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.52055</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.38413</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.41061</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.29565</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.50966</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.43525</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.40626</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.42956</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.43648</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.35623</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.37231</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.37741</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.38442</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.40144</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.3995</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.38337</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.38359</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.41358</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.53753</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41491</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.54191</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4461</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40513</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.39536</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.37927</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.09828</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.55212</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.92525</v>
+      </c>
+      <c r="G126" t="n">
+        <v>1.13761</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.86814</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.29147</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.6025499999999999</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.67841</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.66159</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.54038</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.5700599999999999</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.49824</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.47599</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.40529</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.4813</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.5308099999999999</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.56798</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37227</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.29473</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.30988</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.45147</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.5092300000000001</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.47738</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.3815</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.45448</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.53062</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.2062</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.3068</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.44746</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.18122</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29826</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.02948</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.37414</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.36303</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.39537</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.36205</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.39302</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.39372</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.37307</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.39388</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.50947</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.43062</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.68421</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.38994</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.30839</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.46235</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30224</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3141</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.19388</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30296</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.20932</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.17834</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.20409</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.17568</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.17047</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.29238</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.19942</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.19546</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.36749</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.24413</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.17462</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.24631</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.23224</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.20097</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.30796</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34742</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.17685</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.29901</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.37285</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.18664</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.25213</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.3748</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26915</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28629</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.2889</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.28488</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29032</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.27652</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.27518</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29625</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30046</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30021</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.28807</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.29483</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.29671</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.40859</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.38033</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37248</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.28209</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24306</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.27707</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.28634</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.29688</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29423</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.29972</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34592</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30129</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29279</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29252</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29133</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29133</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.29582</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29623</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.28784</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28126</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29853</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28661</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28556</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.28393</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31286</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.32133</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.37447</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34021</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28443</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28436</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.28351</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.30737</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32851</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37418</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3167</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28136</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30107</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.30637</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30048</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28172</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.28972</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29195</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30311</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29256</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.30893</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30667</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.3005</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.41039</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.15178</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.42173</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6898</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.50236</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.4834</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.38047</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.44623</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.51032</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38332</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5705800000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27577</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.31814</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.29762</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.42502</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.26183</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.40087</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.74464</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.50115</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.41801</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.44088</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41898</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40402</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.55728</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.42409</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.42327</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.45679</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.44892</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.4394</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.38868</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.48752</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.7290399999999999</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47664</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.43042</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50552</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.48234</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.74311</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.3834</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.25701</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.48776</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.2508</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.3884</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.28809</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28002</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.21756</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.27999</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.3819</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28194</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27479</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.27533</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.27325</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.18794</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18061</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27225</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27029</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27123</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27137</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27015</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.18231</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.17975</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.14115</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.22898</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28786</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.25752</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.17949</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.18528</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.23593</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.19142</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.15334</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.14527</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.2115</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.23455</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.29311</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.36714</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.28201</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.28871</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.25463</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.29782</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29431</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29101</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.29972</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.2925</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.28731</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29108</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.26161</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.30185</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.30551</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.24768</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28243</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.26733</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.2673</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.27961</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28208</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.22893</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27103</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33812</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.23126</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.17597</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.22597</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31785</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.28902</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.27569</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.04408</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31489</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28077</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.26901</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28162</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.27682</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.2789</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.27877</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28152</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.26813</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28533</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27012</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.27929</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.26976</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.26763</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.28877</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.29979</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30469</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30324</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30208</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35348</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32346</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31761</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.31909</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3409</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32582</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32663</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.4033</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.61948</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5174500000000001</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.19199</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30747</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29319</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.31906</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31583</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.39592</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31059</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.34542</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.35643</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.33581</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.44204</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.48884</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6511699999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60949</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6562899999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8085399999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.41078</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.44577</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.30872</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31088</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32666</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.3559</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30354</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.27892</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.28703</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.26948</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.27588</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.44511</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40451</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41621</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.45071</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.48665</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.52715</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.56992</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.31723</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41462</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.42062</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.68599</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40525</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.82582</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.52604</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.36656</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3658</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.30769</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.28367</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.28753</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.30323</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.73017</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.58625</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6403099999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.3045</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.31337</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.30598</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.30652</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.25212</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.27861</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.28255</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.30584</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.03091</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.26852</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.2780899999999999</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.26749</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.2749</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36729</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.36785</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.41342</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.48847</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.3945</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.43095</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.43376</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42341</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.29921</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37576</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.24372</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.43964</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37593</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.37885</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.24875</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.24449</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.27158</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.28958</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.25535</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35354</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.28277</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.19129</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.2986</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.20112</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.20816</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.19994</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.23746</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.1894</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.2839</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.27622</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.22603</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.27001</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.21157</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.15305</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.03221</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25713</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.0339</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.03311</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.15331</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.18905</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.15208</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.03268</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.14334</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.14755</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.18509</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.14537</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.1479</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.15044</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.03262</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.15298</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.03267</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.16316</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.17162</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.13631</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28121</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.32332</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.27649</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.27582</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.27283</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.39825</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.00268</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.38501</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.3420899999999999</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.29158</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.27998</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.34082</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28818</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.31104</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.24177</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.27977</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.27305</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.20763</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.25668</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.24425</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.23516</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.25261</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.24881</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.17396</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.18047</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.25267</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.16461</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.28073</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.17068</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22174</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.28254</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.27739</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.27811</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.26785</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.01871</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.17393</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.17111</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.25931</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.18666</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.20997</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.20085</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.008619999999999999</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.18114</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.15651</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.04414</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24034</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.00564</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.01086</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.16938</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02213</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01249</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04299</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04090999999999999</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02937</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.0431</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00608</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04927</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03403</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.00125</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03444</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.21437</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.27342</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28609</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.28331</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.29531</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.29399</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.3055</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.27571</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29124</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.30554</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31156</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.28446</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30628</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29538</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.25771</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.26634</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.26763</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.28312</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.25751</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.25925</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26424</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.14156</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.13815</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.14207</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.13977</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.13625</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.12652</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41075</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.16344</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.26465</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.21187</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.21766</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85388</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86322</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.0851</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.23915</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32316</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28359</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28427</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.651</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29696</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00295</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00213</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.07008</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25452</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47586</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.57211</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.49717</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7363200000000001</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.94984</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.58673</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.38985</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.8100700000000001</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.80829</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9093300000000001</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.3858</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.29776</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.29216</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.27311</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.46541</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.27076</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.24883</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35287</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.24497</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.16146</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.24585</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.23901</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.23309</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.19657</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.22042</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.18082</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.14053</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.17677</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.13569</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.13808</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.12481</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.15351</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.20804</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.28694</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.24961</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.21982</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.22769</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.24066</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.26611</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32119</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37313</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.27004</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.3067</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.2588</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.3267</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31594</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.3112200000000001</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3237</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32473</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31638</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.31942</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.38398</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33605</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39384</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.25019</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.31332</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.29984</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.30477</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.29643</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.28665</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28014</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.28171</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35469</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.3422</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.32229</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3159</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.30478</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.30372</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.29934</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31139</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.28323</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.30531</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.29218</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.56191</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.27233</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.42942</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.29498</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.3616</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.32974</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45753</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.42311</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.47512</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.09642000000000001</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.81748</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.80263</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40354</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.39679</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.53843</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.65216</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8644400000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.3971</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.53806</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.32407</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.30501</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.31168</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.31849</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19368</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.30901</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.3141</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38937</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.31234</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.30553</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.30438</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31074</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.28578</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.29464</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.29463</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33267</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.32722</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.35677</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39093</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43454</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37961</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.33845</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33343</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36638</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50974</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.50928</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.05838</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.8078200000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.53734</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.69045</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.4705299999999999</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.5626100000000001</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.50254</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.42477</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.66735</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.62195</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.01584</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.83413</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.7130299999999999</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.57613</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.40166</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33426</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32511</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.31366</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.27472</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.28642</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28024</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.31972</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28316</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28068</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31518</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.27399</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.27903</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.26963</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.29707</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32468</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.36628</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.2589</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.41896</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.52146</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.1974</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32504</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29485</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.30346</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43463</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.48677</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.33474</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.3098399999999999</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.33737</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32134</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.42406</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.51176</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.46049</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5496599999999999</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.44317</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.42934</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.39383</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45339</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.5445599999999999</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.47214</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.40654</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.41469</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.31496</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3011</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.31706</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39535</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.4485</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42051</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.3462</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33922</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32536</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.34058</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33566</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35672</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.3571</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34425</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.32454</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.37869</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.25899</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.4713</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.49341</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.50828</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.46113</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.47877</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.52512</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36691</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.34674</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34314</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.41938</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36842</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36457</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41996</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.50307</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.41396</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40683</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39171</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33292</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.39037</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.3722200000000001</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35391</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33573</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33465</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.3071</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17618</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29595</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14584</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19877</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14771</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.28701</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04858</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.1222</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22696</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26014</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14247</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14609</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28343</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18656</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22697</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.28108</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.16499</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36488</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.17574</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.30664</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20768</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.16748</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.30489</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.43884</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.49666</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.41956</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.67813</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.44271</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.46359</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38997</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.40576</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.46007</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.40874</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.5301</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.41272</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.48881</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.56569</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.5240199999999999</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38486</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.49586</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.48484</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49752</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.41464</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.4001</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36936</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.38983</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36466</v>
       </c>
     </row>
   </sheetData>
